--- a/Result/profitability/6271.xlsx
+++ b/Result/profitability/6271.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.14</v>
       </c>
       <c r="M2" t="n">
-        <v>1.87625</v>
+        <v>1.87125</v>
       </c>
       <c r="N2" t="n">
-        <v>27.5675</v>
+        <v>27.90875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.41</v>
       </c>
       <c r="M3" t="n">
-        <v>1.73625</v>
+        <v>1.82125</v>
       </c>
       <c r="N3" t="n">
-        <v>27.44875</v>
+        <v>28.105</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.49</v>
       </c>
       <c r="M4" t="n">
-        <v>1.69625</v>
+        <v>1.65875</v>
       </c>
       <c r="N4" t="n">
-        <v>27.6625</v>
+        <v>28.08125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.06</v>
       </c>
       <c r="M5" t="n">
-        <v>1.355</v>
+        <v>1.62375</v>
       </c>
       <c r="N5" t="n">
-        <v>27.18875</v>
+        <v>27.75</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.32</v>
       </c>
       <c r="M6" t="n">
-        <v>1.3525</v>
+        <v>1.37875</v>
       </c>
       <c r="N6" t="n">
-        <v>26.4525</v>
+        <v>26.93375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.02</v>
       </c>
       <c r="M7" t="n">
-        <v>1.195</v>
+        <v>1.2275</v>
       </c>
       <c r="N7" t="n">
-        <v>26.32375</v>
+        <v>26.59875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.51</v>
       </c>
       <c r="M8" t="n">
-        <v>1.105</v>
+        <v>1.18</v>
       </c>
       <c r="N8" t="n">
-        <v>26.45625</v>
+        <v>26.84625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1406,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>0.99</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9724999999999999</v>
+        <v>0.9725</v>
       </c>
       <c r="N10" t="n">
         <v>26.36875</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6271</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3153</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2173</v>
+      </c>
+      <c r="E75" t="n">
+        <v>980</v>
+      </c>
+      <c r="F75" t="n">
+        <v>31.09</v>
+      </c>
+      <c r="G75" t="n">
+        <v>572</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>18.14%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>80</v>
+      </c>
+      <c r="J75" t="n">
+        <v>652</v>
+      </c>
+      <c r="K75" t="n">
+        <v>520</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.045</v>
+      </c>
+      <c r="N75" t="n">
+        <v>27.96625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.6000000000000003</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3174603174603177</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.120000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1115480872363246</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>6.323529411764706</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.489999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1687969924812029</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
